--- a/worklist_template0821.xlsx
+++ b/worklist_template0821.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivint\OneDrive\Desktop\Kelly_Lab\.venv\worklist_git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01c1829094dbd390/Desktop/Kelly_Lab/.venv/worklist_git/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5910DDBE-A351-4778-9C6F-3554FF582AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/worklist_template0821.xlsx
+++ b/worklist_template0821.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01c1829094dbd390/Desktop/Kelly_Lab/.venv/worklist_git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5910DDBE-A351-4778-9C6F-3554FF582AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{5910DDBE-A351-4778-9C6F-3554FF582AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2A751C-6458-4A75-B8C6-A08B2AF144D1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{12DA0CF9-A1F3-4B47-B73A-18ED55D7EBC7}"/>
   </bookViews>
   <sheets>
-    <sheet name="User" sheetId="1" r:id="rId1"/>
-    <sheet name="Manager" sheetId="2" r:id="rId2"/>
+    <sheet name="Experiment" sheetId="1" r:id="rId1"/>
+    <sheet name="Machine" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3995,11 +3995,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="str">
-        <f>IF(LEN(User!AE2)=0,"",User!AE2)</f>
+        <f>IF(LEN(Experiment!AE2)=0,"",Experiment!AE2)</f>
         <v>Condition</v>
       </c>
       <c r="C2" s="7">
-        <f>IF(LEN(User!AF2)=0,"",User!AF2)</f>
+        <f>IF(LEN(Experiment!AF2)=0,"",Experiment!AF2)</f>
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
@@ -4027,7 +4027,7 @@
         <v>52</v>
       </c>
       <c r="L2" s="29">
-        <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
+        <f>IF(LEN(Experiment!AG2)=0,"",Experiment!AG2)</f>
         <v>1</v>
       </c>
       <c r="M2" s="12">
@@ -4047,11 +4047,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="str">
-        <f>IF(LEN(User!AE3)=0,"",User!AE3)</f>
+        <f>IF(LEN(Experiment!AE3)=0,"",Experiment!AE3)</f>
         <v>Condition</v>
       </c>
       <c r="C3" s="7">
-        <f>IF(LEN(User!AF3)=0,"",User!AF3)</f>
+        <f>IF(LEN(Experiment!AF3)=0,"",Experiment!AF3)</f>
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -4079,7 +4079,7 @@
         <v>52</v>
       </c>
       <c r="L3" s="29">
-        <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
+        <f>IF(LEN(Experiment!AG3)=0,"",Experiment!AG3)</f>
         <v>1</v>
       </c>
       <c r="M3" s="12">
@@ -4093,11 +4093,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="str">
-        <f>IF(LEN(User!AE4)=0,"",User!AE4)</f>
+        <f>IF(LEN(Experiment!AE4)=0,"",Experiment!AE4)</f>
         <v>Condition</v>
       </c>
       <c r="C4" s="7">
-        <f>IF(LEN(User!AF4)=0,"",User!AF4)</f>
+        <f>IF(LEN(Experiment!AF4)=0,"",Experiment!AF4)</f>
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -4125,7 +4125,7 @@
         <v>52</v>
       </c>
       <c r="L4" s="29">
-        <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
+        <f>IF(LEN(Experiment!AG4)=0,"",Experiment!AG4)</f>
         <v>1</v>
       </c>
       <c r="M4" s="12">
@@ -4141,11 +4141,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="str">
-        <f>IF(LEN(User!AE5)=0,"",User!AE5)</f>
+        <f>IF(LEN(Experiment!AE5)=0,"",Experiment!AE5)</f>
         <v>Condition</v>
       </c>
       <c r="C5" s="7">
-        <f>IF(LEN(User!AF5)=0,"",User!AF5)</f>
+        <f>IF(LEN(Experiment!AF5)=0,"",Experiment!AF5)</f>
         <v>4</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -4173,7 +4173,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="29">
-        <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
+        <f>IF(LEN(Experiment!AG5)=0,"",Experiment!AG5)</f>
         <v>1</v>
       </c>
       <c r="M5" s="12">
@@ -4193,11 +4193,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="str">
-        <f>IF(LEN(User!AE6)=0,"",User!AE6)</f>
+        <f>IF(LEN(Experiment!AE6)=0,"",Experiment!AE6)</f>
         <v>Condition</v>
       </c>
       <c r="C6" s="7">
-        <f>IF(LEN(User!AF6)=0,"",User!AF6)</f>
+        <f>IF(LEN(Experiment!AF6)=0,"",Experiment!AF6)</f>
         <v>5</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -4225,7 +4225,7 @@
         <v>52</v>
       </c>
       <c r="L6" s="29">
-        <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
+        <f>IF(LEN(Experiment!AG6)=0,"",Experiment!AG6)</f>
         <v>1</v>
       </c>
       <c r="M6" s="12">
@@ -4243,11 +4243,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="str">
-        <f>IF(LEN(User!AE7)=0,"",User!AE7)</f>
+        <f>IF(LEN(Experiment!AE7)=0,"",Experiment!AE7)</f>
         <v>Condition</v>
       </c>
       <c r="C7" s="7">
-        <f>IF(LEN(User!AF7)=0,"",User!AF7)</f>
+        <f>IF(LEN(Experiment!AF7)=0,"",Experiment!AF7)</f>
         <v>6</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -4275,7 +4275,7 @@
         <v>52</v>
       </c>
       <c r="L7" s="29">
-        <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
+        <f>IF(LEN(Experiment!AG7)=0,"",Experiment!AG7)</f>
         <v>1</v>
       </c>
       <c r="M7" s="12">
@@ -4295,11 +4295,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="str">
-        <f>IF(LEN(User!AE8)=0,"",User!AE8)</f>
+        <f>IF(LEN(Experiment!AE8)=0,"",Experiment!AE8)</f>
         <v>Condition</v>
       </c>
       <c r="C8" s="7">
-        <f>IF(LEN(User!AF8)=0,"",User!AF8)</f>
+        <f>IF(LEN(Experiment!AF8)=0,"",Experiment!AF8)</f>
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -4327,7 +4327,7 @@
         <v>52</v>
       </c>
       <c r="L8" s="29">
-        <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
+        <f>IF(LEN(Experiment!AG8)=0,"",Experiment!AG8)</f>
         <v>1</v>
       </c>
       <c r="M8" s="12">
@@ -4341,11 +4341,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="str">
-        <f>IF(LEN(User!AE9)=0,"",User!AE9)</f>
+        <f>IF(LEN(Experiment!AE9)=0,"",Experiment!AE9)</f>
         <v>Condition</v>
       </c>
       <c r="C9" s="7">
-        <f>IF(LEN(User!AF9)=0,"",User!AF9)</f>
+        <f>IF(LEN(Experiment!AF9)=0,"",Experiment!AF9)</f>
         <v>8</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -4373,7 +4373,7 @@
         <v>52</v>
       </c>
       <c r="L9" s="29">
-        <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
+        <f>IF(LEN(Experiment!AG9)=0,"",Experiment!AG9)</f>
         <v>1</v>
       </c>
       <c r="M9" s="12">
@@ -4387,11 +4387,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f>IF(LEN(User!AE10)=0,"",User!AE10)</f>
+        <f>IF(LEN(Experiment!AE10)=0,"",Experiment!AE10)</f>
         <v>Condition</v>
       </c>
       <c r="C10" s="7">
-        <f>IF(LEN(User!AF10)=0,"",User!AF10)</f>
+        <f>IF(LEN(Experiment!AF10)=0,"",Experiment!AF10)</f>
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -4419,7 +4419,7 @@
         <v>52</v>
       </c>
       <c r="L10" s="29">
-        <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
+        <f>IF(LEN(Experiment!AG10)=0,"",Experiment!AG10)</f>
         <v>1</v>
       </c>
       <c r="M10" s="12">
@@ -4433,11 +4433,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="str">
-        <f>IF(LEN(User!AE11)=0,"",User!AE11)</f>
+        <f>IF(LEN(Experiment!AE11)=0,"",Experiment!AE11)</f>
         <v>Condition</v>
       </c>
       <c r="C11" s="7">
-        <f>IF(LEN(User!AF11)=0,"",User!AF11)</f>
+        <f>IF(LEN(Experiment!AF11)=0,"",Experiment!AF11)</f>
         <v>10</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -4465,7 +4465,7 @@
         <v>52</v>
       </c>
       <c r="L11" s="29">
-        <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
+        <f>IF(LEN(Experiment!AG11)=0,"",Experiment!AG11)</f>
         <v>1</v>
       </c>
       <c r="M11" s="12">
@@ -4479,11 +4479,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="str">
-        <f>IF(LEN(User!AE12)=0,"",User!AE12)</f>
+        <f>IF(LEN(Experiment!AE12)=0,"",Experiment!AE12)</f>
         <v>Condition</v>
       </c>
       <c r="C12" s="7">
-        <f>IF(LEN(User!AF12)=0,"",User!AF12)</f>
+        <f>IF(LEN(Experiment!AF12)=0,"",Experiment!AF12)</f>
         <v>11</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -4511,7 +4511,7 @@
         <v>52</v>
       </c>
       <c r="L12" s="29">
-        <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
+        <f>IF(LEN(Experiment!AG12)=0,"",Experiment!AG12)</f>
         <v>1</v>
       </c>
       <c r="M12" s="12">
@@ -4525,11 +4525,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="str">
-        <f>IF(LEN(User!AE13)=0,"",User!AE13)</f>
+        <f>IF(LEN(Experiment!AE13)=0,"",Experiment!AE13)</f>
         <v>Condition</v>
       </c>
       <c r="C13" s="7">
-        <f>IF(LEN(User!AF13)=0,"",User!AF13)</f>
+        <f>IF(LEN(Experiment!AF13)=0,"",Experiment!AF13)</f>
         <v>12</v>
       </c>
       <c r="D13" s="9" t="s">
@@ -4557,7 +4557,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="29">
-        <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
+        <f>IF(LEN(Experiment!AG13)=0,"",Experiment!AG13)</f>
         <v>1</v>
       </c>
       <c r="M13" s="12">
@@ -4571,11 +4571,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="str">
-        <f>IF(LEN(User!AE14)=0,"",User!AE14)</f>
+        <f>IF(LEN(Experiment!AE14)=0,"",Experiment!AE14)</f>
         <v>Condition</v>
       </c>
       <c r="C14" s="7">
-        <f>IF(LEN(User!AF14)=0,"",User!AF14)</f>
+        <f>IF(LEN(Experiment!AF14)=0,"",Experiment!AF14)</f>
         <v>13</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -4603,7 +4603,7 @@
         <v>52</v>
       </c>
       <c r="L14" s="29">
-        <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
+        <f>IF(LEN(Experiment!AG14)=0,"",Experiment!AG14)</f>
         <v>1</v>
       </c>
       <c r="M14" s="12">
@@ -4617,11 +4617,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="str">
-        <f>IF(LEN(User!AE15)=0,"",User!AE15)</f>
+        <f>IF(LEN(Experiment!AE15)=0,"",Experiment!AE15)</f>
         <v>Condition</v>
       </c>
       <c r="C15" s="7">
-        <f>IF(LEN(User!AF15)=0,"",User!AF15)</f>
+        <f>IF(LEN(Experiment!AF15)=0,"",Experiment!AF15)</f>
         <v>14</v>
       </c>
       <c r="D15" s="9" t="s">
@@ -4649,7 +4649,7 @@
         <v>52</v>
       </c>
       <c r="L15" s="29">
-        <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
+        <f>IF(LEN(Experiment!AG15)=0,"",Experiment!AG15)</f>
         <v>1</v>
       </c>
       <c r="M15" s="12">
@@ -4663,11 +4663,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="str">
-        <f>IF(LEN(User!AE16)=0,"",User!AE16)</f>
+        <f>IF(LEN(Experiment!AE16)=0,"",Experiment!AE16)</f>
         <v>Condition</v>
       </c>
       <c r="C16" s="7">
-        <f>IF(LEN(User!AF16)=0,"",User!AF16)</f>
+        <f>IF(LEN(Experiment!AF16)=0,"",Experiment!AF16)</f>
         <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
@@ -4695,7 +4695,7 @@
         <v>52</v>
       </c>
       <c r="L16" s="29">
-        <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
+        <f>IF(LEN(Experiment!AG16)=0,"",Experiment!AG16)</f>
         <v>1</v>
       </c>
       <c r="M16" s="12">
@@ -4709,11 +4709,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="str">
-        <f>IF(LEN(User!AE17)=0,"",User!AE17)</f>
+        <f>IF(LEN(Experiment!AE17)=0,"",Experiment!AE17)</f>
         <v>Condition</v>
       </c>
       <c r="C17" s="7">
-        <f>IF(LEN(User!AF17)=0,"",User!AF17)</f>
+        <f>IF(LEN(Experiment!AF17)=0,"",Experiment!AF17)</f>
         <v>16</v>
       </c>
       <c r="D17" s="9" t="s">
@@ -4741,7 +4741,7 @@
         <v>52</v>
       </c>
       <c r="L17" s="29">
-        <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
+        <f>IF(LEN(Experiment!AG17)=0,"",Experiment!AG17)</f>
         <v>1</v>
       </c>
       <c r="M17" s="12">
@@ -4755,11 +4755,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="str">
-        <f>IF(LEN(User!AE18)=0,"",User!AE18)</f>
+        <f>IF(LEN(Experiment!AE18)=0,"",Experiment!AE18)</f>
         <v>Condition</v>
       </c>
       <c r="C18" s="7">
-        <f>IF(LEN(User!AF18)=0,"",User!AF18)</f>
+        <f>IF(LEN(Experiment!AF18)=0,"",Experiment!AF18)</f>
         <v>17</v>
       </c>
       <c r="D18" s="9" t="s">
@@ -4787,7 +4787,7 @@
         <v>52</v>
       </c>
       <c r="L18" s="29">
-        <f>IF(LEN(User!AG18)=0,"",User!AG18)</f>
+        <f>IF(LEN(Experiment!AG18)=0,"",Experiment!AG18)</f>
         <v>1</v>
       </c>
       <c r="M18" s="12">
@@ -4801,11 +4801,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="str">
-        <f>IF(LEN(User!AE19)=0,"",User!AE19)</f>
+        <f>IF(LEN(Experiment!AE19)=0,"",Experiment!AE19)</f>
         <v>Condition</v>
       </c>
       <c r="C19" s="7">
-        <f>IF(LEN(User!AF19)=0,"",User!AF19)</f>
+        <f>IF(LEN(Experiment!AF19)=0,"",Experiment!AF19)</f>
         <v>18</v>
       </c>
       <c r="D19" s="9" t="s">
@@ -4833,7 +4833,7 @@
         <v>52</v>
       </c>
       <c r="L19" s="29">
-        <f>IF(LEN(User!AG19)=0,"",User!AG19)</f>
+        <f>IF(LEN(Experiment!AG19)=0,"",Experiment!AG19)</f>
         <v>1</v>
       </c>
       <c r="M19" s="12">
@@ -4847,11 +4847,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="str">
-        <f>IF(LEN(User!AE20)=0,"",User!AE20)</f>
+        <f>IF(LEN(Experiment!AE20)=0,"",Experiment!AE20)</f>
         <v>Condition</v>
       </c>
       <c r="C20" s="7">
-        <f>IF(LEN(User!AF20)=0,"",User!AF20)</f>
+        <f>IF(LEN(Experiment!AF20)=0,"",Experiment!AF20)</f>
         <v>19</v>
       </c>
       <c r="D20" s="9" t="s">
@@ -4879,7 +4879,7 @@
         <v>52</v>
       </c>
       <c r="L20" s="29">
-        <f>IF(LEN(User!AG20)=0,"",User!AG20)</f>
+        <f>IF(LEN(Experiment!AG20)=0,"",Experiment!AG20)</f>
         <v>1</v>
       </c>
       <c r="M20" s="12">
@@ -4893,11 +4893,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="str">
-        <f>IF(LEN(User!AE21)=0,"",User!AE21)</f>
+        <f>IF(LEN(Experiment!AE21)=0,"",Experiment!AE21)</f>
         <v>Condition</v>
       </c>
       <c r="C21" s="7">
-        <f>IF(LEN(User!AF21)=0,"",User!AF21)</f>
+        <f>IF(LEN(Experiment!AF21)=0,"",Experiment!AF21)</f>
         <v>20</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -4925,7 +4925,7 @@
         <v>52</v>
       </c>
       <c r="L21" s="29">
-        <f>IF(LEN(User!AG21)=0,"",User!AG21)</f>
+        <f>IF(LEN(Experiment!AG21)=0,"",Experiment!AG21)</f>
         <v>1</v>
       </c>
       <c r="M21" s="12">
@@ -4939,11 +4939,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="str">
-        <f>IF(LEN(User!AE22)=0,"",User!AE22)</f>
+        <f>IF(LEN(Experiment!AE22)=0,"",Experiment!AE22)</f>
         <v>Condition</v>
       </c>
       <c r="C22" s="7">
-        <f>IF(LEN(User!AF22)=0,"",User!AF22)</f>
+        <f>IF(LEN(Experiment!AF22)=0,"",Experiment!AF22)</f>
         <v>21</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -4971,7 +4971,7 @@
         <v>52</v>
       </c>
       <c r="L22" s="29">
-        <f>IF(LEN(User!AG22)=0,"",User!AG22)</f>
+        <f>IF(LEN(Experiment!AG22)=0,"",Experiment!AG22)</f>
         <v>1</v>
       </c>
       <c r="M22" s="12">
@@ -4985,11 +4985,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="str">
-        <f>IF(LEN(User!AE23)=0,"",User!AE23)</f>
+        <f>IF(LEN(Experiment!AE23)=0,"",Experiment!AE23)</f>
         <v>Condition</v>
       </c>
       <c r="C23" s="7">
-        <f>IF(LEN(User!AF23)=0,"",User!AF23)</f>
+        <f>IF(LEN(Experiment!AF23)=0,"",Experiment!AF23)</f>
         <v>22</v>
       </c>
       <c r="D23" s="9" t="s">
@@ -5017,7 +5017,7 @@
         <v>52</v>
       </c>
       <c r="L23" s="29">
-        <f>IF(LEN(User!AG23)=0,"",User!AG23)</f>
+        <f>IF(LEN(Experiment!AG23)=0,"",Experiment!AG23)</f>
         <v>1</v>
       </c>
       <c r="M23" s="12">
@@ -5031,11 +5031,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="str">
-        <f>IF(LEN(User!AE24)=0,"",User!AE24)</f>
+        <f>IF(LEN(Experiment!AE24)=0,"",Experiment!AE24)</f>
         <v>Condition</v>
       </c>
       <c r="C24" s="7">
-        <f>IF(LEN(User!AF24)=0,"",User!AF24)</f>
+        <f>IF(LEN(Experiment!AF24)=0,"",Experiment!AF24)</f>
         <v>23</v>
       </c>
       <c r="D24" s="9" t="s">
@@ -5063,7 +5063,7 @@
         <v>52</v>
       </c>
       <c r="L24" s="29">
-        <f>IF(LEN(User!AG24)=0,"",User!AG24)</f>
+        <f>IF(LEN(Experiment!AG24)=0,"",Experiment!AG24)</f>
         <v>1</v>
       </c>
       <c r="M24" s="12">
@@ -5077,11 +5077,11 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="str">
-        <f>IF(LEN(User!AE25)=0,"",User!AE25)</f>
+        <f>IF(LEN(Experiment!AE25)=0,"",Experiment!AE25)</f>
         <v>Condition</v>
       </c>
       <c r="C25" s="7">
-        <f>IF(LEN(User!AF25)=0,"",User!AF25)</f>
+        <f>IF(LEN(Experiment!AF25)=0,"",Experiment!AF25)</f>
         <v>24</v>
       </c>
       <c r="D25" s="9" t="s">
@@ -5109,7 +5109,7 @@
         <v>52</v>
       </c>
       <c r="L25" s="29">
-        <f>IF(LEN(User!AG25)=0,"",User!AG25)</f>
+        <f>IF(LEN(Experiment!AG25)=0,"",Experiment!AG25)</f>
         <v>1</v>
       </c>
       <c r="M25" s="12">
@@ -5123,11 +5123,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="str">
-        <f>IF(LEN(User!AE26)=0,"",User!AE26)</f>
+        <f>IF(LEN(Experiment!AE26)=0,"",Experiment!AE26)</f>
         <v>Condition</v>
       </c>
       <c r="C26" s="7">
-        <f>IF(LEN(User!AF26)=0,"",User!AF26)</f>
+        <f>IF(LEN(Experiment!AF26)=0,"",Experiment!AF26)</f>
         <v>25</v>
       </c>
       <c r="D26" s="9" t="s">
@@ -5155,7 +5155,7 @@
         <v>52</v>
       </c>
       <c r="L26" s="29">
-        <f>IF(LEN(User!AG26)=0,"",User!AG26)</f>
+        <f>IF(LEN(Experiment!AG26)=0,"",Experiment!AG26)</f>
         <v>1</v>
       </c>
       <c r="M26" s="12">
@@ -5169,11 +5169,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="str">
-        <f>IF(LEN(User!AE27)=0,"",User!AE27)</f>
+        <f>IF(LEN(Experiment!AE27)=0,"",Experiment!AE27)</f>
         <v>Condition</v>
       </c>
       <c r="C27" s="7">
-        <f>IF(LEN(User!AF27)=0,"",User!AF27)</f>
+        <f>IF(LEN(Experiment!AF27)=0,"",Experiment!AF27)</f>
         <v>26</v>
       </c>
       <c r="D27" s="9" t="s">
@@ -5201,7 +5201,7 @@
         <v>52</v>
       </c>
       <c r="L27" s="29">
-        <f>IF(LEN(User!AG27)=0,"",User!AG27)</f>
+        <f>IF(LEN(Experiment!AG27)=0,"",Experiment!AG27)</f>
         <v>1</v>
       </c>
       <c r="M27" s="12">
@@ -5215,11 +5215,11 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="str">
-        <f>IF(LEN(User!AE28)=0,"",User!AE28)</f>
+        <f>IF(LEN(Experiment!AE28)=0,"",Experiment!AE28)</f>
         <v>Condition</v>
       </c>
       <c r="C28" s="7">
-        <f>IF(LEN(User!AF28)=0,"",User!AF28)</f>
+        <f>IF(LEN(Experiment!AF28)=0,"",Experiment!AF28)</f>
         <v>27</v>
       </c>
       <c r="D28" s="9" t="s">
@@ -5247,7 +5247,7 @@
         <v>52</v>
       </c>
       <c r="L28" s="29">
-        <f>IF(LEN(User!AG28)=0,"",User!AG28)</f>
+        <f>IF(LEN(Experiment!AG28)=0,"",Experiment!AG28)</f>
         <v>1</v>
       </c>
       <c r="M28" s="12">
@@ -5261,11 +5261,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="str">
-        <f>IF(LEN(User!AE29)=0,"",User!AE29)</f>
+        <f>IF(LEN(Experiment!AE29)=0,"",Experiment!AE29)</f>
         <v>Condition</v>
       </c>
       <c r="C29" s="7">
-        <f>IF(LEN(User!AF29)=0,"",User!AF29)</f>
+        <f>IF(LEN(Experiment!AF29)=0,"",Experiment!AF29)</f>
         <v>28</v>
       </c>
       <c r="D29" s="9" t="s">
@@ -5293,7 +5293,7 @@
         <v>52</v>
       </c>
       <c r="L29" s="29">
-        <f>IF(LEN(User!AG29)=0,"",User!AG29)</f>
+        <f>IF(LEN(Experiment!AG29)=0,"",Experiment!AG29)</f>
         <v>1</v>
       </c>
       <c r="M29" s="12">
@@ -5307,11 +5307,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="str">
-        <f>IF(LEN(User!AE30)=0,"",User!AE30)</f>
+        <f>IF(LEN(Experiment!AE30)=0,"",Experiment!AE30)</f>
         <v>Condition</v>
       </c>
       <c r="C30" s="7">
-        <f>IF(LEN(User!AF30)=0,"",User!AF30)</f>
+        <f>IF(LEN(Experiment!AF30)=0,"",Experiment!AF30)</f>
         <v>29</v>
       </c>
       <c r="D30" s="9" t="s">
@@ -5339,7 +5339,7 @@
         <v>52</v>
       </c>
       <c r="L30" s="29">
-        <f>IF(LEN(User!AG30)=0,"",User!AG30)</f>
+        <f>IF(LEN(Experiment!AG30)=0,"",Experiment!AG30)</f>
         <v>1</v>
       </c>
       <c r="M30" s="12">
@@ -5353,11 +5353,11 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="str">
-        <f>IF(LEN(User!AE31)=0,"",User!AE31)</f>
+        <f>IF(LEN(Experiment!AE31)=0,"",Experiment!AE31)</f>
         <v>QC</v>
       </c>
       <c r="C31" s="7">
-        <f>IF(LEN(User!AF31)=0,"",User!AF31)</f>
+        <f>IF(LEN(Experiment!AF31)=0,"",Experiment!AF31)</f>
         <v>30</v>
       </c>
       <c r="D31" s="9" t="s">
@@ -5385,7 +5385,7 @@
         <v>52</v>
       </c>
       <c r="L31" s="29">
-        <f>IF(LEN(User!AG31)=0,"",User!AG31)</f>
+        <f>IF(LEN(Experiment!AG31)=0,"",Experiment!AG31)</f>
         <v>1</v>
       </c>
       <c r="M31" s="12" t="s">
@@ -5406,11 +5406,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="str">
-        <f>IF(LEN(User!AE32)=0,"",User!AE32)</f>
+        <f>IF(LEN(Experiment!AE32)=0,"",Experiment!AE32)</f>
         <v>WetQC</v>
       </c>
       <c r="C32" s="7" t="str">
-        <f>IF(LEN(User!AF32)=0,"",User!AF32)</f>
+        <f>IF(LEN(Experiment!AF32)=0,"",Experiment!AF32)</f>
         <v>QC</v>
       </c>
       <c r="D32" s="9" t="s">
@@ -5438,7 +5438,7 @@
         <v>52</v>
       </c>
       <c r="L32" s="29">
-        <f>IF(LEN(User!AG32)=0,"",User!AG32)</f>
+        <f>IF(LEN(Experiment!AG32)=0,"",Experiment!AG32)</f>
         <v>3</v>
       </c>
       <c r="M32" s="12" t="s">
@@ -5459,11 +5459,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="str">
-        <f>IF(LEN(User!AE33)=0,"",User!AE33)</f>
+        <f>IF(LEN(Experiment!AE33)=0,"",Experiment!AE33)</f>
         <v>TrueBlank</v>
       </c>
       <c r="C33" s="7" t="str">
-        <f>IF(LEN(User!AF33)=0,"",User!AF33)</f>
+        <f>IF(LEN(Experiment!AF33)=0,"",Experiment!AF33)</f>
         <v>TrueBlank</v>
       </c>
       <c r="D33" s="9" t="s">
@@ -5491,7 +5491,7 @@
         <v>52</v>
       </c>
       <c r="L33" s="29">
-        <f>IF(LEN(User!AG33)=0,"",User!AG33)</f>
+        <f>IF(LEN(Experiment!AG33)=0,"",Experiment!AG33)</f>
         <v>1</v>
       </c>
       <c r="M33" s="12" t="s">
@@ -5515,7 +5515,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="7">
-        <f>IF(LEN(User!AF34)=0,"",User!AF34)</f>
+        <f>IF(LEN(Experiment!AF34)=0,"",Experiment!AF34)</f>
         <v>67</v>
       </c>
       <c r="D34" s="9" t="s">
@@ -5543,7 +5543,7 @@
         <v>52</v>
       </c>
       <c r="L34" s="29">
-        <f>IF(LEN(User!AG34)=0,"",User!AG34)</f>
+        <f>IF(LEN(Experiment!AG34)=0,"",Experiment!AG34)</f>
         <v>1</v>
       </c>
       <c r="M34" s="12">
@@ -5557,11 +5557,11 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="str">
-        <f>IF(LEN(User!AE35)=0,"",User!AE35)</f>
+        <f>IF(LEN(Experiment!AE35)=0,"",Experiment!AE35)</f>
         <v/>
       </c>
       <c r="C35" s="7" t="str">
-        <f>IF(LEN(User!AF35)=0,"",User!AF35)</f>
+        <f>IF(LEN(Experiment!AF35)=0,"",Experiment!AF35)</f>
         <v/>
       </c>
       <c r="D35" s="30"/>
@@ -5573,7 +5573,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="12"/>
       <c r="L35" s="29" t="str">
-        <f>IF(LEN(User!AG35)=0,"",User!AG35)</f>
+        <f>IF(LEN(Experiment!AG35)=0,"",Experiment!AG35)</f>
         <v/>
       </c>
       <c r="M35" s="12"/>
@@ -5585,11 +5585,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="str">
-        <f>IF(LEN(User!AE36)=0,"",User!AE36)</f>
+        <f>IF(LEN(Experiment!AE36)=0,"",Experiment!AE36)</f>
         <v/>
       </c>
       <c r="C36" s="7" t="str">
-        <f>IF(LEN(User!AF36)=0,"",User!AF36)</f>
+        <f>IF(LEN(Experiment!AF36)=0,"",Experiment!AF36)</f>
         <v/>
       </c>
       <c r="D36" s="30"/>
@@ -5601,7 +5601,7 @@
       <c r="J36" s="11"/>
       <c r="K36" s="12"/>
       <c r="L36" s="29" t="str">
-        <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
+        <f>IF(LEN(Experiment!AG36)=0,"",Experiment!AG36)</f>
         <v/>
       </c>
       <c r="N36" s="12"/>
@@ -5612,11 +5612,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="str">
-        <f>IF(LEN(User!AE37)=0,"",User!AE37)</f>
+        <f>IF(LEN(Experiment!AE37)=0,"",Experiment!AE37)</f>
         <v/>
       </c>
       <c r="C37" s="7" t="str">
-        <f>IF(LEN(User!AF37)=0,"",User!AF37)</f>
+        <f>IF(LEN(Experiment!AF37)=0,"",Experiment!AF37)</f>
         <v/>
       </c>
       <c r="D37" s="30"/>
@@ -5628,7 +5628,7 @@
       <c r="J37" s="11"/>
       <c r="K37" s="12"/>
       <c r="L37" s="29" t="str">
-        <f>IF(LEN(User!AG37)=0,"",User!AG37)</f>
+        <f>IF(LEN(Experiment!AG37)=0,"",Experiment!AG37)</f>
         <v/>
       </c>
       <c r="M37" s="12"/>
@@ -5640,11 +5640,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="str">
-        <f>IF(LEN(User!AE38)=0,"",User!AE38)</f>
+        <f>IF(LEN(Experiment!AE38)=0,"",Experiment!AE38)</f>
         <v/>
       </c>
       <c r="C38" s="7" t="str">
-        <f>IF(LEN(User!AF38)=0,"",User!AF38)</f>
+        <f>IF(LEN(Experiment!AF38)=0,"",Experiment!AF38)</f>
         <v/>
       </c>
       <c r="D38" s="30"/>
@@ -5656,7 +5656,7 @@
       <c r="J38" s="11"/>
       <c r="K38" s="12"/>
       <c r="L38" s="29" t="str">
-        <f>IF(LEN(User!AG38)=0,"",User!AG38)</f>
+        <f>IF(LEN(Experiment!AG38)=0,"",Experiment!AG38)</f>
         <v/>
       </c>
       <c r="M38" s="12"/>
@@ -5668,11 +5668,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="str">
-        <f>IF(LEN(User!AE39)=0,"",User!AE39)</f>
+        <f>IF(LEN(Experiment!AE39)=0,"",Experiment!AE39)</f>
         <v/>
       </c>
       <c r="C39" s="7" t="str">
-        <f>IF(LEN(User!AF39)=0,"",User!AF39)</f>
+        <f>IF(LEN(Experiment!AF39)=0,"",Experiment!AF39)</f>
         <v/>
       </c>
       <c r="D39" s="30"/>
@@ -5684,7 +5684,7 @@
       <c r="J39" s="11"/>
       <c r="K39" s="12"/>
       <c r="L39" s="29" t="str">
-        <f>IF(LEN(User!AG39)=0,"",User!AG39)</f>
+        <f>IF(LEN(Experiment!AG39)=0,"",Experiment!AG39)</f>
         <v/>
       </c>
       <c r="M39" s="12"/>
@@ -5696,11 +5696,11 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="str">
-        <f>IF(LEN(User!AE40)=0,"",User!AE40)</f>
+        <f>IF(LEN(Experiment!AE40)=0,"",Experiment!AE40)</f>
         <v/>
       </c>
       <c r="C40" s="7" t="str">
-        <f>IF(LEN(User!AF40)=0,"",User!AF40)</f>
+        <f>IF(LEN(Experiment!AF40)=0,"",Experiment!AF40)</f>
         <v/>
       </c>
       <c r="D40" s="30"/>
@@ -5712,7 +5712,7 @@
       <c r="J40" s="11"/>
       <c r="K40" s="12"/>
       <c r="L40" s="29" t="str">
-        <f>IF(LEN(User!AG40)=0,"",User!AG40)</f>
+        <f>IF(LEN(Experiment!AG40)=0,"",Experiment!AG40)</f>
         <v/>
       </c>
       <c r="M40" s="12"/>
@@ -5724,11 +5724,11 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="str">
-        <f>IF(LEN(User!AE41)=0,"",User!AE41)</f>
+        <f>IF(LEN(Experiment!AE41)=0,"",Experiment!AE41)</f>
         <v/>
       </c>
       <c r="C41" s="7" t="str">
-        <f>IF(LEN(User!AF41)=0,"",User!AF41)</f>
+        <f>IF(LEN(Experiment!AF41)=0,"",Experiment!AF41)</f>
         <v/>
       </c>
       <c r="D41" s="30"/>
@@ -5740,7 +5740,7 @@
       <c r="J41" s="11"/>
       <c r="K41" s="12"/>
       <c r="L41" s="29" t="str">
-        <f>IF(LEN(User!AG41)=0,"",User!AG41)</f>
+        <f>IF(LEN(Experiment!AG41)=0,"",Experiment!AG41)</f>
         <v/>
       </c>
       <c r="M41" s="12"/>
@@ -5752,11 +5752,11 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="str">
-        <f>IF(LEN(User!AE42)=0,"",User!AE42)</f>
+        <f>IF(LEN(Experiment!AE42)=0,"",Experiment!AE42)</f>
         <v/>
       </c>
       <c r="C42" s="7" t="str">
-        <f>IF(LEN(User!AF42)=0,"",User!AF42)</f>
+        <f>IF(LEN(Experiment!AF42)=0,"",Experiment!AF42)</f>
         <v/>
       </c>
       <c r="D42" s="30"/>
@@ -5768,7 +5768,7 @@
       <c r="J42" s="11"/>
       <c r="K42" s="12"/>
       <c r="L42" s="29" t="str">
-        <f>IF(LEN(User!AG42)=0,"",User!AG42)</f>
+        <f>IF(LEN(Experiment!AG42)=0,"",Experiment!AG42)</f>
         <v/>
       </c>
       <c r="M42" s="12"/>
@@ -5780,11 +5780,11 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="str">
-        <f>IF(LEN(User!AE43)=0,"",User!AE43)</f>
+        <f>IF(LEN(Experiment!AE43)=0,"",Experiment!AE43)</f>
         <v/>
       </c>
       <c r="C43" s="7" t="str">
-        <f>IF(LEN(User!AF43)=0,"",User!AF43)</f>
+        <f>IF(LEN(Experiment!AF43)=0,"",Experiment!AF43)</f>
         <v/>
       </c>
       <c r="D43" s="30"/>
@@ -5796,7 +5796,7 @@
       <c r="J43" s="11"/>
       <c r="K43" s="12"/>
       <c r="L43" s="29" t="str">
-        <f>IF(LEN(User!AG43)=0,"",User!AG43)</f>
+        <f>IF(LEN(Experiment!AG43)=0,"",Experiment!AG43)</f>
         <v/>
       </c>
       <c r="M43" s="12"/>
@@ -5808,11 +5808,11 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="str">
-        <f>IF(LEN(User!AE44)=0,"",User!AE44)</f>
+        <f>IF(LEN(Experiment!AE44)=0,"",Experiment!AE44)</f>
         <v/>
       </c>
       <c r="C44" s="7" t="str">
-        <f>IF(LEN(User!AF44)=0,"",User!AF44)</f>
+        <f>IF(LEN(Experiment!AF44)=0,"",Experiment!AF44)</f>
         <v/>
       </c>
       <c r="D44" s="30"/>
@@ -5824,7 +5824,7 @@
       <c r="J44" s="11"/>
       <c r="K44" s="12"/>
       <c r="L44" s="29" t="str">
-        <f>IF(LEN(User!AG44)=0,"",User!AG44)</f>
+        <f>IF(LEN(Experiment!AG44)=0,"",Experiment!AG44)</f>
         <v/>
       </c>
       <c r="M44" s="12"/>
@@ -5836,11 +5836,11 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="str">
-        <f>IF(LEN(User!AE45)=0,"",User!AE45)</f>
+        <f>IF(LEN(Experiment!AE45)=0,"",Experiment!AE45)</f>
         <v/>
       </c>
       <c r="C45" s="7" t="str">
-        <f>IF(LEN(User!AF45)=0,"",User!AF45)</f>
+        <f>IF(LEN(Experiment!AF45)=0,"",Experiment!AF45)</f>
         <v/>
       </c>
       <c r="D45" s="30"/>
@@ -5852,7 +5852,7 @@
       <c r="J45" s="11"/>
       <c r="K45" s="12"/>
       <c r="L45" s="29" t="str">
-        <f>IF(LEN(User!AG45)=0,"",User!AG45)</f>
+        <f>IF(LEN(Experiment!AG45)=0,"",Experiment!AG45)</f>
         <v/>
       </c>
       <c r="M45" s="12"/>
@@ -5864,11 +5864,11 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="str">
-        <f>IF(LEN(User!AE46)=0,"",User!AE46)</f>
+        <f>IF(LEN(Experiment!AE46)=0,"",Experiment!AE46)</f>
         <v/>
       </c>
       <c r="C46" s="7" t="str">
-        <f>IF(LEN(User!AF46)=0,"",User!AF46)</f>
+        <f>IF(LEN(Experiment!AF46)=0,"",Experiment!AF46)</f>
         <v/>
       </c>
       <c r="D46" s="30"/>
@@ -5880,7 +5880,7 @@
       <c r="J46" s="11"/>
       <c r="K46" s="12"/>
       <c r="L46" s="29" t="str">
-        <f>IF(LEN(User!AG46)=0,"",User!AG46)</f>
+        <f>IF(LEN(Experiment!AG46)=0,"",Experiment!AG46)</f>
         <v/>
       </c>
       <c r="M46" s="12"/>
@@ -5892,11 +5892,11 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="str">
-        <f>IF(LEN(User!AE47)=0,"",User!AE47)</f>
+        <f>IF(LEN(Experiment!AE47)=0,"",Experiment!AE47)</f>
         <v/>
       </c>
       <c r="C47" s="7" t="str">
-        <f>IF(LEN(User!AF47)=0,"",User!AF47)</f>
+        <f>IF(LEN(Experiment!AF47)=0,"",Experiment!AF47)</f>
         <v/>
       </c>
       <c r="D47" s="30"/>
@@ -5908,7 +5908,7 @@
       <c r="J47" s="11"/>
       <c r="K47" s="12"/>
       <c r="L47" s="29" t="str">
-        <f>IF(LEN(User!AG47)=0,"",User!AG47)</f>
+        <f>IF(LEN(Experiment!AG47)=0,"",Experiment!AG47)</f>
         <v/>
       </c>
       <c r="M47" s="12"/>
@@ -5920,11 +5920,11 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="str">
-        <f>IF(LEN(User!AE48)=0,"",User!AE48)</f>
+        <f>IF(LEN(Experiment!AE48)=0,"",Experiment!AE48)</f>
         <v/>
       </c>
       <c r="C48" s="7" t="str">
-        <f>IF(LEN(User!AF48)=0,"",User!AF48)</f>
+        <f>IF(LEN(Experiment!AF48)=0,"",Experiment!AF48)</f>
         <v/>
       </c>
       <c r="D48" s="31"/>
@@ -5936,7 +5936,7 @@
       <c r="J48" s="11"/>
       <c r="K48" s="12"/>
       <c r="L48" s="29" t="str">
-        <f>IF(LEN(User!AG48)=0,"",User!AG48)</f>
+        <f>IF(LEN(Experiment!AG48)=0,"",Experiment!AG48)</f>
         <v/>
       </c>
       <c r="M48" s="12"/>
@@ -5948,11 +5948,11 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="str">
-        <f>IF(LEN(User!AE49)=0,"",User!AE49)</f>
+        <f>IF(LEN(Experiment!AE49)=0,"",Experiment!AE49)</f>
         <v/>
       </c>
       <c r="C49" s="7" t="str">
-        <f>IF(LEN(User!AF49)=0,"",User!AF49)</f>
+        <f>IF(LEN(Experiment!AF49)=0,"",Experiment!AF49)</f>
         <v/>
       </c>
       <c r="D49" s="31"/>
@@ -5964,7 +5964,7 @@
       <c r="J49" s="11"/>
       <c r="K49" s="12"/>
       <c r="L49" s="29" t="str">
-        <f>IF(LEN(User!AG49)=0,"",User!AG49)</f>
+        <f>IF(LEN(Experiment!AG49)=0,"",Experiment!AG49)</f>
         <v/>
       </c>
       <c r="M49" s="12"/>
@@ -5976,11 +5976,11 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="str">
-        <f>IF(LEN(User!AE50)=0,"",User!AE50)</f>
+        <f>IF(LEN(Experiment!AE50)=0,"",Experiment!AE50)</f>
         <v/>
       </c>
       <c r="C50" s="7" t="str">
-        <f>IF(LEN(User!AF50)=0,"",User!AF50)</f>
+        <f>IF(LEN(Experiment!AF50)=0,"",Experiment!AF50)</f>
         <v/>
       </c>
       <c r="D50" s="31"/>
@@ -5992,7 +5992,7 @@
       <c r="J50" s="11"/>
       <c r="K50" s="12"/>
       <c r="L50" s="29" t="str">
-        <f>IF(LEN(User!AG50)=0,"",User!AG50)</f>
+        <f>IF(LEN(Experiment!AG50)=0,"",Experiment!AG50)</f>
         <v/>
       </c>
       <c r="M50" s="12"/>
@@ -6004,11 +6004,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="17" t="str">
-        <f>IF(LEN(User!AE51)=0,"",User!AE51)</f>
+        <f>IF(LEN(Experiment!AE51)=0,"",Experiment!AE51)</f>
         <v/>
       </c>
       <c r="C51" s="13" t="str">
-        <f>IF(LEN(User!AF51)=0,"",User!AF51)</f>
+        <f>IF(LEN(Experiment!AF51)=0,"",Experiment!AF51)</f>
         <v/>
       </c>
       <c r="D51" s="9"/>
